--- a/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20222.xlsx
+++ b/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20222.xlsx
@@ -646,16 +646,19 @@
         <v>42</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>42</v>
       </c>
-      <c r="E2">
-        <v>42</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -669,16 +672,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -692,16 +698,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -715,16 +724,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -738,16 +750,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +827,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -838,7 +853,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -864,7 +879,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -890,7 +905,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -916,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20222.xlsx
+++ b/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20222.xlsx
@@ -827,7 +827,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -931,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
